--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2448,15 +2448,15 @@
         <v/>
       </c>
       <c r="I29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,2,0),V29))</f>
         <v/>
       </c>
       <c r="J29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,3,0),W29))</f>
         <v/>
       </c>
       <c r="K29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,4,0),X29))</f>
         <v/>
       </c>
       <c r="S29" s="19" t="n">
@@ -2467,6 +2467,15 @@
       </c>
       <c r="U29" s="19" t="n">
         <v>0.10005</v>
+      </c>
+      <c r="V29" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W29" s="20" t="n">
+        <v>95.03</v>
+      </c>
+      <c r="X29" s="20" t="n">
+        <v>197.12</v>
       </c>
     </row>
     <row r="30">
@@ -6065,7 +6074,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2507,15 +2507,15 @@
         <v/>
       </c>
       <c r="I30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,2,0),V30))</f>
         <v/>
       </c>
       <c r="J30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,3,0),W30))</f>
         <v/>
       </c>
       <c r="K30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,4,0),X30))</f>
         <v/>
       </c>
       <c r="S30" s="19" t="n">
@@ -2526,6 +2526,15 @@
       </c>
       <c r="U30" s="19" t="n">
         <v>0.08304</v>
+      </c>
+      <c r="V30" s="20" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="W30" s="20" t="n">
+        <v>120.35</v>
+      </c>
+      <c r="X30" s="20" t="n">
+        <v>226.83</v>
       </c>
     </row>
     <row r="31">
@@ -6074,7 +6083,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2566,15 +2566,15 @@
         <v/>
       </c>
       <c r="I31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,2,0),V31))</f>
         <v/>
       </c>
       <c r="J31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,3,0),W31))</f>
         <v/>
       </c>
       <c r="K31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,4,0),X31))</f>
         <v/>
       </c>
       <c r="S31" s="19" t="n">
@@ -2585,6 +2585,15 @@
       </c>
       <c r="U31" s="19" t="n">
         <v>0.10093</v>
+      </c>
+      <c r="V31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="20" t="n">
+        <v>110.86</v>
+      </c>
+      <c r="X31" s="20" t="n">
+        <v>214</v>
       </c>
     </row>
     <row r="32">
@@ -6083,7 +6092,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6138,7 +6147,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>117.6</v>
+        <v>122.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6169,7 +6178,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>115.5</v>
+        <v>119.4</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6200,7 +6209,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>118.07</v>
+        <v>124.5</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6231,7 +6240,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>118.07</v>
+        <v>121.5</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6262,7 +6271,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>99.28</v>
+        <v>111.28</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6293,7 +6302,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>94.12</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6319,7 +6328,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>117.2</v>
+        <v>121.77</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6345,7 +6354,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>96.47</v>
+        <v>98.5</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6371,7 +6380,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>52.93</v>
+        <v>52.94</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6397,7 +6406,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>75.83</v>
+        <v>77</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6423,7 +6432,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6449,7 +6458,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>66.26000000000001</v>
+        <v>66.91</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6475,7 +6484,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>43.2</v>
+        <v>43.85</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6501,7 +6510,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>75.25</v>
+        <v>76.3</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6527,7 +6536,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>59.15</v>
+        <v>59.8</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6553,7 +6562,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>54.17</v>
+        <v>54.1</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2625,15 +2625,15 @@
         <v/>
       </c>
       <c r="I32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,2,0),V32))</f>
         <v/>
       </c>
       <c r="J32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,3,0),W32))</f>
         <v/>
       </c>
       <c r="K32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,4,0),X32))</f>
         <v/>
       </c>
       <c r="S32" s="19" t="n">
@@ -2644,6 +2644,15 @@
       </c>
       <c r="U32" s="19" t="n">
         <v>0.04494</v>
+      </c>
+      <c r="V32" s="20" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="W32" s="20" t="n">
+        <v>110.84</v>
+      </c>
+      <c r="X32" s="20" t="n">
+        <v>188.55</v>
       </c>
     </row>
     <row r="33">
@@ -6092,7 +6101,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6147,7 +6156,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>122.5</v>
+        <v>125.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6178,7 +6187,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>119.4</v>
+        <v>118</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6209,7 +6218,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>124.5</v>
+        <v>122</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6240,7 +6249,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>121.5</v>
+        <v>120.96</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6271,7 +6280,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>111.28</v>
+        <v>111.78</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6302,7 +6311,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>96.15000000000001</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6328,7 +6337,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>121.77</v>
+        <v>120.3</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6354,7 +6363,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6380,7 +6389,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>52.94</v>
+        <v>52.25</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6406,7 +6415,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>77</v>
+        <v>76.3</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6432,7 +6441,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>77</v>
+        <v>76.3</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6458,7 +6467,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>66.91</v>
+        <v>66.86</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6484,7 +6493,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>43.85</v>
+        <v>43.8</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6510,7 +6519,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>76.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6536,7 +6545,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>59.8</v>
+        <v>59.75</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6562,7 +6571,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>54.1</v>
+        <v>54</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2684,15 +2684,15 @@
         <v/>
       </c>
       <c r="I33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,2,0),V33))</f>
         <v/>
       </c>
       <c r="J33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,3,0),W33))</f>
         <v/>
       </c>
       <c r="K33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,4,0),X33))</f>
         <v/>
       </c>
       <c r="S33" s="19" t="n">
@@ -2703,6 +2703,15 @@
       </c>
       <c r="U33" s="19" t="n">
         <v>0.02598</v>
+      </c>
+      <c r="V33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="20" t="n">
+        <v>103.78</v>
+      </c>
+      <c r="X33" s="20" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="34">
@@ -6101,7 +6110,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6156,7 +6165,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>125.5</v>
+        <v>125</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6187,7 +6196,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>118</v>
+        <v>117.85</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6218,7 +6227,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>122</v>
+        <v>124.27</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6249,7 +6258,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>120.96</v>
+        <v>120.99</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6280,7 +6289,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>111.78</v>
+        <v>113.28</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6311,7 +6320,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>96.65000000000001</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6337,7 +6346,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>120.3</v>
+        <v>121</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6363,7 +6372,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>99</v>
+        <v>100.5</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6389,7 +6398,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>52.25</v>
+        <v>49.75</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6415,7 +6424,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>76.3</v>
+        <v>75.69</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6441,7 +6450,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>76.3</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6467,7 +6476,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>66.86</v>
+        <v>65.61</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6493,7 +6502,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>43.8</v>
+        <v>42.55</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6519,7 +6528,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>75.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6545,7 +6554,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>59.75</v>
+        <v>58.5</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2743,15 +2743,15 @@
         <v/>
       </c>
       <c r="I34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,2,0),V34))</f>
         <v/>
       </c>
       <c r="J34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,3,0),W34))</f>
         <v/>
       </c>
       <c r="K34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,4,0),X34))</f>
         <v/>
       </c>
       <c r="S34" s="19" t="n">
@@ -2762,6 +2762,15 @@
       </c>
       <c r="U34" s="19" t="n">
         <v>0.01711</v>
+      </c>
+      <c r="V34" s="20" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="W34" s="20" t="n">
+        <v>103.37</v>
+      </c>
+      <c r="X34" s="20" t="n">
+        <v>217</v>
       </c>
     </row>
     <row r="35">
@@ -6110,7 +6119,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6165,7 +6174,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>125</v>
+        <v>126.25</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6196,7 +6205,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>117.85</v>
+        <v>117.5</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6227,7 +6236,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>124.27</v>
+        <v>124.47</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6258,7 +6267,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>120.99</v>
+        <v>121.15</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6289,7 +6298,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>113.28</v>
+        <v>113.53</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6320,7 +6329,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>98.15000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6372,7 +6381,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>100.5</v>
+        <v>100.75</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6398,7 +6407,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>49.75</v>
+        <v>49.7</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6424,7 +6433,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>75.69</v>
+        <v>76.31</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6450,7 +6459,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>74.34999999999999</v>
+        <v>76.31</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6476,7 +6485,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>65.61</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6502,7 +6511,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>42.55</v>
+        <v>42.65</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6528,7 +6537,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>75</v>
+        <v>75.7</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6554,7 +6563,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2802,15 +2802,15 @@
         <v/>
       </c>
       <c r="I35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,2,0),V35))</f>
         <v/>
       </c>
       <c r="J35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,3,0),W35))</f>
         <v/>
       </c>
       <c r="K35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,4,0),X35))</f>
         <v/>
       </c>
       <c r="S35" s="19" t="n">
@@ -2821,6 +2821,15 @@
       </c>
       <c r="U35" s="19" t="n">
         <v>0.07488</v>
+      </c>
+      <c r="V35" s="20" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="W35" s="20" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="X35" s="20" t="n">
+        <v>212.82</v>
       </c>
     </row>
     <row r="36">

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2861,15 +2861,15 @@
         <v/>
       </c>
       <c r="I36" s="17">
-        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,2,0),V36))</f>
         <v/>
       </c>
       <c r="J36" s="17">
-        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,3,0),W36))</f>
         <v/>
       </c>
       <c r="K36" s="17">
-        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,4,0),X36))</f>
         <v/>
       </c>
       <c r="S36" s="19" t="n">
@@ -2880,6 +2880,15 @@
       </c>
       <c r="U36" s="19" t="n">
         <v>0.07197000000000001</v>
+      </c>
+      <c r="V36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="20" t="n">
+        <v>106.51</v>
+      </c>
+      <c r="X36" s="20" t="n">
+        <v>217</v>
       </c>
     </row>
     <row r="37">
@@ -3360,15 +3369,15 @@
         <v>46235</v>
       </c>
       <c r="B49" s="14">
-        <f>IFERROR(VLOOKUP($A49,PQ_Mensual!$A:$D,2,0),"")</f>
+        <f>IFERROR(VLOOKUP($A49,PQ_Mensual!$A:$D,2,0),S49)</f>
         <v/>
       </c>
       <c r="C49" s="14">
-        <f>IFERROR(VLOOKUP($A49,PQ_Mensual!$A:$D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP($A49,PQ_Mensual!$A:$D,3,0),T49)</f>
         <v/>
       </c>
       <c r="D49" s="14">
-        <f>IFERROR(VLOOKUP($A49,PQ_Mensual!$A:$D,4,0),"")</f>
+        <f>IFERROR(VLOOKUP($A49,PQ_Mensual!$A:$D,4,0),U49)</f>
         <v/>
       </c>
       <c r="E49" s="14">
@@ -3378,6 +3387,15 @@
       <c r="F49" s="15">
         <f>IF(E49="","",E49*1000)</f>
         <v/>
+      </c>
+      <c r="S49" s="19" t="n">
+        <v>0.10001</v>
+      </c>
+      <c r="T49" s="19" t="n">
+        <v>0.10395</v>
+      </c>
+      <c r="U49" s="19" t="n">
+        <v>0.13164</v>
       </c>
     </row>
     <row r="50">
@@ -5573,16 +5591,16 @@
       <c r="B49" s="28" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="14">
-        <f>IFERROR(VLOOKUP($A49,PQ_Mensual6P!$A:$G,4,0),"")</f>
+        <f>IFERROR(VLOOKUP($A49,PQ_Mensual6P!$A:$G,4,0),U49)</f>
         <v/>
       </c>
       <c r="E49" s="14">
-        <f>IFERROR(VLOOKUP($A49,PQ_Mensual6P!$A:$G,5,0),"")</f>
+        <f>IFERROR(VLOOKUP($A49,PQ_Mensual6P!$A:$G,5,0),V49)</f>
         <v/>
       </c>
       <c r="F49" s="28" t="n"/>
       <c r="G49" s="14">
-        <f>IFERROR(VLOOKUP($A49,PQ_Mensual6P!$A:$G,7,0),"")</f>
+        <f>IFERROR(VLOOKUP($A49,PQ_Mensual6P!$A:$G,7,0),X49)</f>
         <v/>
       </c>
       <c r="H49" s="15">
@@ -5593,6 +5611,15 @@
         <is>
           <t>MEDIA</t>
         </is>
+      </c>
+      <c r="U49" s="19" t="n">
+        <v>0.10352</v>
+      </c>
+      <c r="V49" s="19" t="n">
+        <v>0.09999</v>
+      </c>
+      <c r="X49" s="19" t="n">
+        <v>0.13164</v>
       </c>
     </row>
     <row r="50">
@@ -6128,7 +6155,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="I3" s="8">
-        <f>IFERROR(DATE(YEAR(MAX(PQ_Diario!A:A)),MONTH(MAX(PQ_Diario!A:A)),1),DATE(2026,8,1))</f>
+        <f>IFERROR(DATE(YEAR(MAX(PQ_Diario!A:A)),MONTH(MAX(PQ_Diario!A:A)),1),DATE(2026,9,1))</f>
         <v/>
       </c>
     </row>
@@ -1016,13 +1016,13 @@
         <v>0.04928</v>
       </c>
       <c r="V6" s="20" t="n">
-        <v>0.29</v>
+        <v>24.75</v>
       </c>
       <c r="W6" s="20" t="n">
-        <v>111.68</v>
+        <v>141.55</v>
       </c>
       <c r="X6" s="20" t="n">
-        <v>198.69</v>
+        <v>238.74</v>
       </c>
     </row>
     <row r="7">
@@ -1083,13 +1083,13 @@
         <v>0.12311</v>
       </c>
       <c r="V7" s="20" t="n">
-        <v>-0.3</v>
+        <v>58.23</v>
       </c>
       <c r="W7" s="20" t="n">
-        <v>106.2</v>
+        <v>159.91</v>
       </c>
       <c r="X7" s="20" t="n">
-        <v>210.3</v>
+        <v>247.27</v>
       </c>
     </row>
     <row r="8">
@@ -1121,15 +1121,15 @@
         <v/>
       </c>
       <c r="I8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,2,0),V8))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,3,0),W8))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,4,0),X8))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q8" s="18">
@@ -1148,15 +1148,6 @@
       </c>
       <c r="U8" s="19" t="n">
         <v>0.08814</v>
-      </c>
-      <c r="V8" s="20" t="n">
-        <v>75</v>
-      </c>
-      <c r="W8" s="20" t="n">
-        <v>151.87</v>
-      </c>
-      <c r="X8" s="20" t="n">
-        <v>222.69</v>
       </c>
     </row>
     <row r="9">
@@ -1188,15 +1179,15 @@
         <v/>
       </c>
       <c r="I9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,2,0),V9))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,3,0),W9))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,4,0),X9))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q9" s="18">
@@ -1215,15 +1206,6 @@
       </c>
       <c r="U9" s="19" t="n">
         <v>0.07088</v>
-      </c>
-      <c r="V9" s="20" t="n">
-        <v>69</v>
-      </c>
-      <c r="W9" s="20" t="n">
-        <v>146.37</v>
-      </c>
-      <c r="X9" s="20" t="n">
-        <v>212.52</v>
       </c>
     </row>
     <row r="10">
@@ -1255,15 +1237,15 @@
         <v/>
       </c>
       <c r="I10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,2,0),V10))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,3,0),W10))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,4,0),X10))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q10" s="18">
@@ -1282,15 +1264,6 @@
       </c>
       <c r="U10" s="19" t="n">
         <v>0.07295</v>
-      </c>
-      <c r="V10" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="W10" s="20" t="n">
-        <v>118.92</v>
-      </c>
-      <c r="X10" s="20" t="n">
-        <v>199.47</v>
       </c>
     </row>
     <row r="11">
@@ -1322,15 +1295,15 @@
         <v/>
       </c>
       <c r="I11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,2,0),V11))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,3,0),W11))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,4,0),X11))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q11" s="18">
@@ -1349,15 +1322,6 @@
       </c>
       <c r="U11" s="19" t="n">
         <v>0.08851000000000001</v>
-      </c>
-      <c r="V11" s="20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W11" s="20" t="n">
-        <v>109.51</v>
-      </c>
-      <c r="X11" s="20" t="n">
-        <v>209.61</v>
       </c>
     </row>
     <row r="12">
@@ -1389,15 +1353,15 @@
         <v/>
       </c>
       <c r="I12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,2,0),V12))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,3,0),W12))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,4,0),X12))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q12" s="18">
@@ -1416,15 +1380,6 @@
       </c>
       <c r="U12" s="19" t="n">
         <v>0.08432000000000001</v>
-      </c>
-      <c r="V12" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="W12" s="20" t="n">
-        <v>119.03</v>
-      </c>
-      <c r="X12" s="20" t="n">
-        <v>220</v>
       </c>
     </row>
     <row r="13">
@@ -1456,15 +1411,15 @@
         <v/>
       </c>
       <c r="I13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,2,0),V13))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,3,0),W13))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,4,0),X13))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q13" s="18">
@@ -1483,15 +1438,6 @@
       </c>
       <c r="U13" s="19" t="n">
         <v>0.09261</v>
-      </c>
-      <c r="V13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="20" t="n">
-        <v>108.61</v>
-      </c>
-      <c r="X13" s="20" t="n">
-        <v>191.01</v>
       </c>
     </row>
     <row r="14">
@@ -1523,15 +1469,15 @@
         <v/>
       </c>
       <c r="I14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,2,0),V14))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,3,0),W14))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,4,0),X14))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q14" s="18">
@@ -1550,15 +1496,6 @@
       </c>
       <c r="U14" s="19" t="n">
         <v>0.09848</v>
-      </c>
-      <c r="V14" s="20" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="W14" s="20" t="n">
-        <v>94.39</v>
-      </c>
-      <c r="X14" s="20" t="n">
-        <v>175.73</v>
       </c>
     </row>
     <row r="15">
@@ -1590,15 +1527,15 @@
         <v/>
       </c>
       <c r="I15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,2,0),V15))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,3,0),W15))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,4,0),X15))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q15" s="18">
@@ -1617,15 +1554,6 @@
       </c>
       <c r="U15" s="19" t="n">
         <v>0.08542</v>
-      </c>
-      <c r="V15" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="W15" s="20" t="n">
-        <v>126.76</v>
-      </c>
-      <c r="X15" s="20" t="n">
-        <v>233.76</v>
       </c>
     </row>
     <row r="16">
@@ -1657,15 +1585,15 @@
         <v/>
       </c>
       <c r="I16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,2,0),V16))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,3,0),W16))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,4,0),X16))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q16" s="18">
@@ -1684,15 +1612,6 @@
       </c>
       <c r="U16" s="19" t="n">
         <v>0.05176</v>
-      </c>
-      <c r="V16" s="20" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="W16" s="20" t="n">
-        <v>128.85</v>
-      </c>
-      <c r="X16" s="20" t="n">
-        <v>235.51</v>
       </c>
     </row>
     <row r="17">
@@ -1724,15 +1643,15 @@
         <v/>
       </c>
       <c r="I17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,2,0),V17))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,3,0),W17))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,4,0),X17))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q17" s="18">
@@ -1751,15 +1670,6 @@
       </c>
       <c r="U17" s="19" t="n">
         <v>0.06365</v>
-      </c>
-      <c r="V17" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="W17" s="20" t="n">
-        <v>135.31</v>
-      </c>
-      <c r="X17" s="20" t="n">
-        <v>250</v>
       </c>
     </row>
     <row r="18">
@@ -1791,15 +1701,15 @@
         <v/>
       </c>
       <c r="I18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,2,0),V18))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,3,0),W18))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,4,0),X18))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q18" s="21">
@@ -1818,15 +1728,6 @@
       </c>
       <c r="U18" s="19" t="n">
         <v>0.06423</v>
-      </c>
-      <c r="V18" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="W18" s="20" t="n">
-        <v>138.9</v>
-      </c>
-      <c r="X18" s="20" t="n">
-        <v>268.97</v>
       </c>
     </row>
     <row r="19">
@@ -1858,15 +1759,15 @@
         <v/>
       </c>
       <c r="I19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,2,0),V19))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,3,0),W19))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,4,0),X19))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S19" s="19" t="n">
@@ -1877,15 +1778,6 @@
       </c>
       <c r="U19" s="19" t="n">
         <v>0.03621</v>
-      </c>
-      <c r="V19" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="W19" s="20" t="n">
-        <v>140.09</v>
-      </c>
-      <c r="X19" s="20" t="n">
-        <v>252.5</v>
       </c>
     </row>
     <row r="20">
@@ -1917,15 +1809,15 @@
         <v/>
       </c>
       <c r="I20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,2,0),V20))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,3,0),W20))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,4,0),X20))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S20" s="19" t="n">
@@ -1936,15 +1828,6 @@
       </c>
       <c r="U20" s="19" t="n">
         <v>0.01494</v>
-      </c>
-      <c r="V20" s="20" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="W20" s="20" t="n">
-        <v>116.51</v>
-      </c>
-      <c r="X20" s="20" t="n">
-        <v>209.95</v>
       </c>
     </row>
     <row r="21">
@@ -1976,15 +1859,15 @@
         <v/>
       </c>
       <c r="I21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,2,0),V21))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,3,0),W21))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,4,0),X21))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S21" s="19" t="n">
@@ -1995,15 +1878,6 @@
       </c>
       <c r="U21" s="19" t="n">
         <v>0.01337</v>
-      </c>
-      <c r="V21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="20" t="n">
-        <v>116.02</v>
-      </c>
-      <c r="X21" s="20" t="n">
-        <v>215.04</v>
       </c>
     </row>
     <row r="22">
@@ -2035,15 +1909,15 @@
         <v/>
       </c>
       <c r="I22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,2,0),V22))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,3,0),W22))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,4,0),X22))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S22" s="19" t="n">
@@ -2054,15 +1928,6 @@
       </c>
       <c r="U22" s="19" t="n">
         <v>0.03306</v>
-      </c>
-      <c r="V22" s="20" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="W22" s="20" t="n">
-        <v>157.35</v>
-      </c>
-      <c r="X22" s="20" t="n">
-        <v>240</v>
       </c>
     </row>
     <row r="23">
@@ -2094,15 +1959,15 @@
         <v/>
       </c>
       <c r="I23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,2,0),V23))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,3,0),W23))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,4,0),X23))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S23" s="19" t="n">
@@ -2113,15 +1978,6 @@
       </c>
       <c r="U23" s="19" t="n">
         <v>0.05189</v>
-      </c>
-      <c r="V23" s="20" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="W23" s="20" t="n">
-        <v>127.64</v>
-      </c>
-      <c r="X23" s="20" t="n">
-        <v>248</v>
       </c>
     </row>
     <row r="24">
@@ -2153,15 +2009,15 @@
         <v/>
       </c>
       <c r="I24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,2,0),V24))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,3,0),W24))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,4,0),X24))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S24" s="19" t="n">
@@ -2172,15 +2028,6 @@
       </c>
       <c r="U24" s="19" t="n">
         <v>0.07045</v>
-      </c>
-      <c r="V24" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="W24" s="20" t="n">
-        <v>127.55</v>
-      </c>
-      <c r="X24" s="20" t="n">
-        <v>216.74</v>
       </c>
     </row>
     <row r="25">
@@ -2212,15 +2059,15 @@
         <v/>
       </c>
       <c r="I25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,2,0),V25))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,3,0),W25))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,4,0),X25))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S25" s="19" t="n">
@@ -2231,15 +2078,6 @@
       </c>
       <c r="U25" s="19" t="n">
         <v>0.08558</v>
-      </c>
-      <c r="V25" s="20" t="n">
-        <v>46.52</v>
-      </c>
-      <c r="W25" s="20" t="n">
-        <v>138.69</v>
-      </c>
-      <c r="X25" s="20" t="n">
-        <v>202.04</v>
       </c>
     </row>
     <row r="26">
@@ -2271,15 +2109,15 @@
         <v/>
       </c>
       <c r="I26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,2,0),V26))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,3,0),W26))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,4,0),X26))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S26" s="19" t="n">
@@ -2290,15 +2128,6 @@
       </c>
       <c r="U26" s="19" t="n">
         <v>0.0725</v>
-      </c>
-      <c r="V26" s="20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W26" s="20" t="n">
-        <v>113.98</v>
-      </c>
-      <c r="X26" s="20" t="n">
-        <v>211.88</v>
       </c>
     </row>
     <row r="27">
@@ -2330,15 +2159,15 @@
         <v/>
       </c>
       <c r="I27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,2,0),V27))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,3,0),W27))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,4,0),X27))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S27" s="19" t="n">
@@ -2349,15 +2178,6 @@
       </c>
       <c r="U27" s="19" t="n">
         <v>0.0595</v>
-      </c>
-      <c r="V27" s="20" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="W27" s="20" t="n">
-        <v>94.56999999999999</v>
-      </c>
-      <c r="X27" s="20" t="n">
-        <v>188</v>
       </c>
     </row>
     <row r="28">
@@ -2389,15 +2209,15 @@
         <v/>
       </c>
       <c r="I28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,2,0),V28))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,3,0),W28))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,4,0),X28))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S28" s="19" t="n">
@@ -2408,15 +2228,6 @@
       </c>
       <c r="U28" s="19" t="n">
         <v>0.09408999999999999</v>
-      </c>
-      <c r="V28" s="20" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="W28" s="20" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="X28" s="20" t="n">
-        <v>166.93</v>
       </c>
     </row>
     <row r="29">
@@ -2448,15 +2259,15 @@
         <v/>
       </c>
       <c r="I29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,2,0),V29))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,3,0),W29))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,4,0),X29))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S29" s="19" t="n">
@@ -2467,15 +2278,6 @@
       </c>
       <c r="U29" s="19" t="n">
         <v>0.10005</v>
-      </c>
-      <c r="V29" s="20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W29" s="20" t="n">
-        <v>95.03</v>
-      </c>
-      <c r="X29" s="20" t="n">
-        <v>197.12</v>
       </c>
     </row>
     <row r="30">
@@ -2507,15 +2309,15 @@
         <v/>
       </c>
       <c r="I30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,2,0),V30))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,3,0),W30))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,4,0),X30))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S30" s="19" t="n">
@@ -2526,15 +2328,6 @@
       </c>
       <c r="U30" s="19" t="n">
         <v>0.08304</v>
-      </c>
-      <c r="V30" s="20" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="W30" s="20" t="n">
-        <v>120.35</v>
-      </c>
-      <c r="X30" s="20" t="n">
-        <v>226.83</v>
       </c>
     </row>
     <row r="31">
@@ -2566,15 +2359,15 @@
         <v/>
       </c>
       <c r="I31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,2,0),V31))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,3,0),W31))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,4,0),X31))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S31" s="19" t="n">
@@ -2585,15 +2378,6 @@
       </c>
       <c r="U31" s="19" t="n">
         <v>0.10093</v>
-      </c>
-      <c r="V31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="20" t="n">
-        <v>110.86</v>
-      </c>
-      <c r="X31" s="20" t="n">
-        <v>214</v>
       </c>
     </row>
     <row r="32">
@@ -2625,15 +2409,15 @@
         <v/>
       </c>
       <c r="I32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,2,0),V32))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,3,0),W32))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,4,0),X32))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S32" s="19" t="n">
@@ -2644,15 +2428,6 @@
       </c>
       <c r="U32" s="19" t="n">
         <v>0.04494</v>
-      </c>
-      <c r="V32" s="20" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="W32" s="20" t="n">
-        <v>110.84</v>
-      </c>
-      <c r="X32" s="20" t="n">
-        <v>188.55</v>
       </c>
     </row>
     <row r="33">
@@ -2684,15 +2459,15 @@
         <v/>
       </c>
       <c r="I33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,2,0),V33))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,3,0),W33))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,4,0),X33))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S33" s="19" t="n">
@@ -2703,15 +2478,6 @@
       </c>
       <c r="U33" s="19" t="n">
         <v>0.02598</v>
-      </c>
-      <c r="V33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="20" t="n">
-        <v>103.78</v>
-      </c>
-      <c r="X33" s="20" t="n">
-        <v>216</v>
       </c>
     </row>
     <row r="34">
@@ -2743,15 +2509,15 @@
         <v/>
       </c>
       <c r="I34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,2,0),V34))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,3,0),W34))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,4,0),X34))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S34" s="19" t="n">
@@ -2762,15 +2528,6 @@
       </c>
       <c r="U34" s="19" t="n">
         <v>0.01711</v>
-      </c>
-      <c r="V34" s="20" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="W34" s="20" t="n">
-        <v>103.37</v>
-      </c>
-      <c r="X34" s="20" t="n">
-        <v>217</v>
       </c>
     </row>
     <row r="35">
@@ -2802,15 +2559,15 @@
         <v/>
       </c>
       <c r="I35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,2,0),V35))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,3,0),W35))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,4,0),X35))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S35" s="19" t="n">
@@ -2821,15 +2578,6 @@
       </c>
       <c r="U35" s="19" t="n">
         <v>0.07488</v>
-      </c>
-      <c r="V35" s="20" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="W35" s="20" t="n">
-        <v>100.98</v>
-      </c>
-      <c r="X35" s="20" t="n">
-        <v>212.82</v>
       </c>
     </row>
     <row r="36">
@@ -2861,15 +2609,15 @@
         <v/>
       </c>
       <c r="I36" s="17">
-        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,2,0),V36))</f>
+        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J36" s="17">
-        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,3,0),W36))</f>
+        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K36" s="17">
-        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,4,0),X36))</f>
+        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S36" s="19" t="n">
@@ -2880,15 +2628,6 @@
       </c>
       <c r="U36" s="19" t="n">
         <v>0.07197000000000001</v>
-      </c>
-      <c r="V36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="20" t="n">
-        <v>106.51</v>
-      </c>
-      <c r="X36" s="20" t="n">
-        <v>217</v>
       </c>
     </row>
     <row r="37">
@@ -6155,7 +5894,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6210,10 +5949,10 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>126.25</v>
+        <v>125.25</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="37" t="inlineStr">
         <is>
@@ -6222,7 +5961,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>FTB M Sep-26</t>
+          <t>FTB M Oct-26</t>
         </is>
       </c>
     </row>
@@ -6241,7 +5980,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>117.5</v>
+        <v>129.16</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6253,7 +5992,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FTB M Oct-26</t>
+          <t>FTB M Nov-26</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6011,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>124.47</v>
+        <v>127.4</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6284,7 +6023,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FTB M Nov-26</t>
+          <t>FTB M Dec-26</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6042,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>121.15</v>
+        <v>122</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6315,7 +6054,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FTB M Dec-26</t>
+          <t>FTB M Jan-27</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6073,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>113.53</v>
+        <v>103.9</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6346,7 +6085,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FTB M Jan-27</t>
+          <t>FTB M Feb-27</t>
         </is>
       </c>
     </row>
@@ -6365,14 +6104,14 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>98.40000000000001</v>
+        <v>93.55</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FTB M Feb-27</t>
+          <t>FTB M Mar-27</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6130,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>121</v>
+        <v>127.25</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6417,7 +6156,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>100.75</v>
+        <v>106.25</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6443,7 +6182,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>49.7</v>
+        <v>50.25</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6469,10 +6208,10 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>76.31</v>
+        <v>78.25</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -6495,7 +6234,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>76.31</v>
+        <v>76.98</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6521,7 +6260,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>65.70999999999999</v>
+        <v>68</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6547,7 +6286,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>42.65</v>
+        <v>42.8</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6573,7 +6312,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>75.7</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6599,7 +6338,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>58.6</v>
+        <v>58.75</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6625,7 +6364,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>54</v>
+        <v>54.25</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1121,15 +1121,15 @@
         <v/>
       </c>
       <c r="I8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,2,0),V8))</f>
         <v/>
       </c>
       <c r="J8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,3,0),W8))</f>
         <v/>
       </c>
       <c r="K8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,4,0),X8))</f>
         <v/>
       </c>
       <c r="Q8" s="18">
@@ -1148,6 +1148,15 @@
       </c>
       <c r="U8" s="19" t="n">
         <v>0.08814</v>
+      </c>
+      <c r="V8" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="W8" s="20" t="n">
+        <v>155.99</v>
+      </c>
+      <c r="X8" s="20" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -5894,7 +5903,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -5949,7 +5958,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>125.25</v>
+        <v>130</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -5980,7 +5989,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>129.16</v>
+        <v>134</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6011,7 +6020,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>127.4</v>
+        <v>132.07</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6042,7 +6051,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>122</v>
+        <v>128.95</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6073,7 +6082,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>103.9</v>
+        <v>107.85</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6130,7 +6139,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>127.25</v>
+        <v>132</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6156,7 +6165,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>106.25</v>
+        <v>110.2</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6182,7 +6191,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>50.25</v>
+        <v>51.87</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6208,7 +6217,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>78.25</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6234,7 +6243,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>76.98</v>
+        <v>77.13</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6260,7 +6269,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>68</v>
+        <v>68.5</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6286,7 +6295,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>42.8</v>
+        <v>44.05</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6312,7 +6321,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>77.84999999999999</v>
+        <v>79</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6338,7 +6347,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>58.75</v>
+        <v>60</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6364,7 +6373,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>54.25</v>
+        <v>54.5</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1188,15 +1188,15 @@
         <v/>
       </c>
       <c r="I9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,2,0),V9))</f>
         <v/>
       </c>
       <c r="J9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,3,0),W9))</f>
         <v/>
       </c>
       <c r="K9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,4,0),X9))</f>
         <v/>
       </c>
       <c r="Q9" s="18">
@@ -1215,6 +1215,15 @@
       </c>
       <c r="U9" s="19" t="n">
         <v>0.07088</v>
+      </c>
+      <c r="V9" s="20" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="W9" s="20" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="X9" s="20" t="n">
+        <v>260.27</v>
       </c>
     </row>
     <row r="10">
@@ -5903,7 +5912,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -5958,7 +5967,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -5989,7 +5998,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>134</v>
+        <v>140.05</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6020,7 +6029,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>132.07</v>
+        <v>137.02</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6051,7 +6060,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>128.95</v>
+        <v>139</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6082,7 +6091,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>107.85</v>
+        <v>111.34</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6139,7 +6148,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>132</v>
+        <v>136.65</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6165,7 +6174,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>110.2</v>
+        <v>114.75</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6191,7 +6200,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>51.87</v>
+        <v>53.98</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6217,7 +6226,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>77.20999999999999</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6243,7 +6252,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>77.13</v>
+        <v>80.25</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6269,7 +6278,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>68.5</v>
+        <v>71</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6295,7 +6304,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>44.05</v>
+        <v>46.55</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6321,7 +6330,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>79</v>
+        <v>82.2</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6347,7 +6356,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6373,7 +6382,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>54.5</v>
+        <v>56</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1255,15 +1255,15 @@
         <v/>
       </c>
       <c r="I10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,2,0),V10))</f>
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,3,0),W10))</f>
         <v/>
       </c>
       <c r="K10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,4,0),X10))</f>
         <v/>
       </c>
       <c r="Q10" s="18">
@@ -1282,6 +1282,15 @@
       </c>
       <c r="U10" s="19" t="n">
         <v>0.07295</v>
+      </c>
+      <c r="V10" s="20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W10" s="20" t="n">
+        <v>138.11</v>
+      </c>
+      <c r="X10" s="20" t="n">
+        <v>225.01</v>
       </c>
     </row>
     <row r="11">
@@ -5912,7 +5921,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -5967,7 +5976,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>133</v>
+        <v>129.94</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -5998,7 +6007,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>140.05</v>
+        <v>137.32</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6029,7 +6038,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>137.02</v>
+        <v>137.07</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6060,7 +6069,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6122,7 +6131,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>93.55</v>
+        <v>89.06</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6148,7 +6157,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>136.65</v>
+        <v>134.75</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6174,7 +6183,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>114.75</v>
+        <v>113.55</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6200,7 +6209,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>53.98</v>
+        <v>53.5</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6226,7 +6235,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>80.23999999999999</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6252,7 +6261,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>80.25</v>
+        <v>80.47</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6278,7 +6287,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>71</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6304,7 +6313,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>46.55</v>
+        <v>45.65</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6330,7 +6339,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>82.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6356,7 +6365,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>62.5</v>
+        <v>61.6</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6382,7 +6391,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1322,15 +1322,15 @@
         <v/>
       </c>
       <c r="I11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,2,0),V11))</f>
         <v/>
       </c>
       <c r="J11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,3,0),W11))</f>
         <v/>
       </c>
       <c r="K11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,4,0),X11))</f>
         <v/>
       </c>
       <c r="Q11" s="18">
@@ -1349,6 +1349,15 @@
       </c>
       <c r="U11" s="19" t="n">
         <v>0.08851000000000001</v>
+      </c>
+      <c r="V11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="20" t="n">
+        <v>140.01</v>
+      </c>
+      <c r="X11" s="20" t="n">
+        <v>249.3</v>
       </c>
     </row>
     <row r="12">
@@ -5921,7 +5930,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -5976,7 +5985,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>129.94</v>
+        <v>129.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6007,7 +6016,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>137.32</v>
+        <v>135.94</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6038,7 +6047,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>137.07</v>
+        <v>135.14</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6069,7 +6078,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>140</v>
+        <v>138.95</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6100,7 +6109,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>111.34</v>
+        <v>124</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6131,7 +6140,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>89.06</v>
+        <v>75.61</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6157,7 +6166,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>134.75</v>
+        <v>133.5</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6183,7 +6192,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>113.55</v>
+        <v>112.5</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6209,7 +6218,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>53.5</v>
+        <v>53.9</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6235,7 +6244,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>78.48999999999999</v>
+        <v>78.02</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6261,7 +6270,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>80.47</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6287,7 +6296,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>70.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6313,7 +6322,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>45.65</v>
+        <v>44.85</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6339,7 +6348,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>81.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6365,7 +6374,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>61.6</v>
+        <v>60.8</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6391,7 +6400,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>56.1</v>
+        <v>57</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1389,15 +1389,15 @@
         <v/>
       </c>
       <c r="I12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,2,0),V12))</f>
         <v/>
       </c>
       <c r="J12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,3,0),W12))</f>
         <v/>
       </c>
       <c r="K12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,4,0),X12))</f>
         <v/>
       </c>
       <c r="Q12" s="18">
@@ -1416,6 +1416,15 @@
       </c>
       <c r="U12" s="19" t="n">
         <v>0.08432000000000001</v>
+      </c>
+      <c r="V12" s="20" t="n">
+        <v>57</v>
+      </c>
+      <c r="W12" s="20" t="n">
+        <v>172.07</v>
+      </c>
+      <c r="X12" s="20" t="n">
+        <v>265</v>
       </c>
     </row>
     <row r="13">
@@ -5930,7 +5939,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1456,15 +1456,15 @@
         <v/>
       </c>
       <c r="I13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,2,0),V13))</f>
         <v/>
       </c>
       <c r="J13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,3,0),W13))</f>
         <v/>
       </c>
       <c r="K13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,4,0),X13))</f>
         <v/>
       </c>
       <c r="Q13" s="18">
@@ -1483,6 +1483,15 @@
       </c>
       <c r="U13" s="19" t="n">
         <v>0.09261</v>
+      </c>
+      <c r="V13" s="20" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="W13" s="20" t="n">
+        <v>151.73</v>
+      </c>
+      <c r="X13" s="20" t="n">
+        <v>230.01</v>
       </c>
     </row>
     <row r="14">
@@ -5939,7 +5948,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1523,15 +1523,15 @@
         <v/>
       </c>
       <c r="I14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,2,0),V14))</f>
         <v/>
       </c>
       <c r="J14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,3,0),W14))</f>
         <v/>
       </c>
       <c r="K14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,4,0),X14))</f>
         <v/>
       </c>
       <c r="Q14" s="18">
@@ -1550,6 +1550,15 @@
       </c>
       <c r="U14" s="19" t="n">
         <v>0.09848</v>
+      </c>
+      <c r="V14" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="20" t="n">
+        <v>107.76</v>
+      </c>
+      <c r="X14" s="20" t="n">
+        <v>212.09</v>
       </c>
     </row>
     <row r="15">
@@ -5948,7 +5957,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6003,7 +6012,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>129.5</v>
+        <v>130.95</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6034,7 +6043,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>135.94</v>
+        <v>137.36</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6065,7 +6074,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>135.14</v>
+        <v>138.11</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6096,7 +6105,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>138.95</v>
+        <v>143.5</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6127,7 +6136,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>124</v>
+        <v>124.99</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6158,7 +6167,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>75.61</v>
+        <v>77.14</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6184,7 +6193,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>133.5</v>
+        <v>135.45</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6210,7 +6219,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>112.5</v>
+        <v>114.9</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6236,7 +6245,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>53.9</v>
+        <v>54.9</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6262,7 +6271,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>78.02</v>
+        <v>78.97</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6288,7 +6297,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>79.98999999999999</v>
+        <v>81.25</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6314,7 +6323,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>69.3</v>
+        <v>69.5</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6340,7 +6349,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>44.85</v>
+        <v>45.05</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6366,7 +6375,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>81</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6392,7 +6401,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>60.8</v>
+        <v>61</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6418,7 +6427,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>57</v>
+        <v>57.75</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1590,15 +1590,15 @@
         <v/>
       </c>
       <c r="I15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,2,0),V15))</f>
         <v/>
       </c>
       <c r="J15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,3,0),W15))</f>
         <v/>
       </c>
       <c r="K15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,4,0),X15))</f>
         <v/>
       </c>
       <c r="Q15" s="18">
@@ -1617,6 +1617,15 @@
       </c>
       <c r="U15" s="19" t="n">
         <v>0.08542</v>
+      </c>
+      <c r="V15" s="20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W15" s="20" t="n">
+        <v>145.21</v>
+      </c>
+      <c r="X15" s="20" t="n">
+        <v>278.48</v>
       </c>
     </row>
     <row r="16">
@@ -5957,7 +5966,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6012,7 +6021,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>130.95</v>
+        <v>133.85</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6043,7 +6052,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>137.36</v>
+        <v>138.57</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6074,7 +6083,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>138.11</v>
+        <v>139.57</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6105,7 +6114,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>143.5</v>
+        <v>145.75</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6136,7 +6145,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>124.99</v>
+        <v>126.16</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6167,7 +6176,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>77.14</v>
+        <v>78.47</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6193,7 +6202,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>135.45</v>
+        <v>137.31</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6219,7 +6228,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>114.9</v>
+        <v>116.5</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6245,7 +6254,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>54.9</v>
+        <v>56.25</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6271,7 +6280,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>78.97</v>
+        <v>82</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6297,7 +6306,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>81.25</v>
+        <v>85.5</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6323,7 +6332,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6349,7 +6358,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>45.05</v>
+        <v>47.05</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6375,7 +6384,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>82.40000000000001</v>
+        <v>84.97</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6401,7 +6410,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6427,7 +6436,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>57.75</v>
+        <v>57.9</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1657,15 +1657,15 @@
         <v/>
       </c>
       <c r="I16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,2,0),V16))</f>
         <v/>
       </c>
       <c r="J16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,3,0),W16))</f>
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,4,0),X16))</f>
         <v/>
       </c>
       <c r="Q16" s="18">
@@ -1684,6 +1684,15 @@
       </c>
       <c r="U16" s="19" t="n">
         <v>0.05176</v>
+      </c>
+      <c r="V16" s="20" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="W16" s="20" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="X16" s="20" t="n">
+        <v>250.01</v>
       </c>
     </row>
     <row r="17">
@@ -5966,7 +5975,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6021,7 +6030,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>133.85</v>
+        <v>139</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6052,7 +6061,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>138.57</v>
+        <v>148.54</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6083,7 +6092,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>139.57</v>
+        <v>150.56</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6114,7 +6123,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>145.75</v>
+        <v>152.75</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6145,7 +6154,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>126.16</v>
+        <v>133.16</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6176,7 +6185,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>78.47</v>
+        <v>85.47</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6202,7 +6211,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>137.31</v>
+        <v>146</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6228,7 +6237,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>116.5</v>
+        <v>123.5</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6254,7 +6263,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>56.25</v>
+        <v>59</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6280,7 +6289,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>82</v>
+        <v>83.61</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6306,7 +6315,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>85.5</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6332,7 +6341,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>72.5</v>
+        <v>73.75</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6358,7 +6367,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>47.05</v>
+        <v>48.3</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6384,7 +6393,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>84.97</v>
+        <v>88.5</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6410,7 +6419,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>63</v>
+        <v>64.25</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6436,7 +6445,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>57.9</v>
+        <v>57.75</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1724,15 +1724,15 @@
         <v/>
       </c>
       <c r="I17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,2,0),V17))</f>
         <v/>
       </c>
       <c r="J17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,3,0),W17))</f>
         <v/>
       </c>
       <c r="K17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,4,0),X17))</f>
         <v/>
       </c>
       <c r="Q17" s="18">
@@ -1751,6 +1751,15 @@
       </c>
       <c r="U17" s="19" t="n">
         <v>0.06365</v>
+      </c>
+      <c r="V17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="20" t="n">
+        <v>118.28</v>
+      </c>
+      <c r="X17" s="20" t="n">
+        <v>213.63</v>
       </c>
     </row>
     <row r="18">
@@ -5975,7 +5984,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6030,7 +6039,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>139</v>
+        <v>139.75</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6061,7 +6070,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>148.54</v>
+        <v>153.59</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6092,7 +6101,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>150.56</v>
+        <v>155.6</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6123,7 +6132,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>152.75</v>
+        <v>157.55</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6154,7 +6163,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>133.16</v>
+        <v>137.96</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6185,7 +6194,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>85.47</v>
+        <v>90.27</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6211,7 +6220,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>146</v>
+        <v>149.6</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6237,7 +6246,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>123.5</v>
+        <v>128.3</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6263,7 +6272,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>59</v>
+        <v>61.65</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6289,7 +6298,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>83.61</v>
+        <v>87.31</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6315,7 +6324,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>88.34999999999999</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6341,7 +6350,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>73.75</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6367,7 +6376,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>48.3</v>
+        <v>49.35</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6393,7 +6402,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>88.5</v>
+        <v>93</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6419,7 +6428,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>64.25</v>
+        <v>65.3</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6445,7 +6454,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>57.75</v>
+        <v>57.7</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>
